--- a/Nhom01/SE_9/SE_9_Nhom01_ClientWishList.xlsx
+++ b/Nhom01/SE_9/SE_9_Nhom01_ClientWishList.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Acceptance criteria theo rubric môn học</t>
+          <t>Tiêu chí nghiệm thu theo yêu cầu môn học</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Each row is an original wish, close to stakeholder words, not a user story; it has RAW ID, source, raw wish and note.</t>
+          <t>Mỗi dòng ghi một mong muốn gốc, gần với lời của bên liên quan và chưa viết thành câu chuyện người dùng; có mã RAW, nguồn, nội dung mong muốn và ghi chú.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Wish List rows 2–13, columns A:E; cột E (Ghi chú) trống ở cả 12 dòng.</t>
+          <t>RAW-001–RAW-012</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Sources include management board, residents, cashier and local authorities, plus documents such as Excel or paper ledger.</t>
+          <t>Nguồn bao gồm Ban quản trị, cư dân, thủ quỹ, cơ quan địa phương và tài liệu như Excel hoặc sổ giấy.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Rows 2–13, B:C</t>
+          <t>RAW-001–RAW-012</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>The list is not prioritized; priority belongs in the backlog.</t>
+          <t>Danh sách không xếp thứ tự ưu tiên; việc ưu tiên được thực hiện trong danh sách công việc sản phẩm.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Rows 1–13</t>
+          <t>RAW-001–RAW-012</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>At least 30 raw requirements are recorded for version 1.0.</t>
+          <t>Mục tiêu môn học yêu cầu ghi nhận ít nhất 30 yêu cầu thô cho phiên bản 1.0.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Rows 2–13</t>
+          <t>RAW-001–RAW-012</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
